--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484061_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484061_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2161</v>
+        <v>4.6203</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6926</v>
+        <v>2.2651</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5235</v>
+        <v>2.3552</v>
       </c>
       <c r="G2" t="n">
         <v>2.7308</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.705</v>
+        <v>-1.3009</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1222</v>
+        <v>-0.5497</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5828</v>
+        <v>-0.7512</v>
       </c>
       <c r="V2" t="n">
         <v>1.2065</v>
@@ -639,13 +639,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5632</v>
+        <v>2.3704</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5285</v>
+        <v>-0.0581</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0918</v>
+        <v>2.4284</v>
       </c>
       <c r="G3" t="n">
         <v>0.8456</v>
@@ -684,13 +684,13 @@
         <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0679</v>
+        <v>-0.2607</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8105</v>
+        <v>-0.34</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2574</v>
+        <v>0.0793</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -717,13 +717,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5632</v>
+        <v>2.3704</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5285</v>
+        <v>-0.0581</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0918</v>
+        <v>2.4284</v>
       </c>
       <c r="G4" t="n">
         <v>0.8456</v>
@@ -762,13 +762,13 @@
         <v>1.7855</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0679</v>
+        <v>-0.2607</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8105</v>
+        <v>-0.34</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2574</v>
+        <v>0.0793</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -783,7 +783,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MAÑES CARRETERO</t>
+          <t>D. TUGORES SOTO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -795,73 +795,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1664</v>
+        <v>1.3941</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4036</v>
+        <v>-1.38</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5701</v>
+        <v>2.774</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.941</v>
+        <v>4.1648</v>
       </c>
       <c r="H5" t="n">
-        <v>0.68</v>
+        <v>2.7617</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.621</v>
+        <v>1.4031</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.1551</v>
+        <v>3.0982</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6409</v>
+        <v>3.211</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.796</v>
+        <v>-0.1128</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2141</v>
+        <v>1.0667</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0391</v>
+        <v>-0.4493</v>
       </c>
       <c r="O5" t="n">
-        <v>0.175</v>
+        <v>1.5159</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1984</v>
+        <v>-2.7774</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>-3.9677</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3136</v>
+        <v>-0.2594</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8047</v>
+        <v>-0.7764</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4911</v>
+        <v>0.5171</v>
       </c>
       <c r="V5" t="n">
-        <v>3.6194</v>
+        <v>0.266</v>
       </c>
       <c r="W5" t="n">
-        <v>3.5481</v>
+        <v>0.266</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. TUGORES SOTO</t>
+          <t>S. SERRATACO SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -873,64 +873,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7833</v>
+        <v>0.9317</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8504</v>
+        <v>1.1248</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6338</v>
+        <v>-0.1932</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1648</v>
+        <v>1.181</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7617</v>
+        <v>0.524</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4031</v>
+        <v>0.657</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0982</v>
+        <v>1.0438</v>
       </c>
       <c r="K6" t="n">
-        <v>3.211</v>
+        <v>0.9635</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1128</v>
+        <v>0.0803</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0667</v>
+        <v>0.1372</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4493</v>
+        <v>-0.4395</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5159</v>
+        <v>0.5767</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.7774</v>
+        <v>0.7935</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8701</v>
+        <v>-2.178</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2469</v>
+        <v>-1.0542</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3768</v>
+        <v>-1.1239</v>
       </c>
       <c r="V6" t="n">
-        <v>0.266</v>
+        <v>1.1352</v>
       </c>
       <c r="W6" t="n">
-        <v>0.266</v>
+        <v>1.1352</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. SERRATACO SANCHEZ</t>
+          <t>E. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -951,73 +951,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4292</v>
+        <v>-0.1879</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8188</v>
+        <v>-0.6077</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3896</v>
+        <v>0.4198</v>
       </c>
       <c r="G7" t="n">
-        <v>1.181</v>
+        <v>-1.941</v>
       </c>
       <c r="H7" t="n">
-        <v>0.524</v>
+        <v>0.68</v>
       </c>
       <c r="I7" t="n">
-        <v>0.657</v>
+        <v>-2.621</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0438</v>
+        <v>-2.1551</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9635</v>
+        <v>0.6409</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0803</v>
+        <v>-2.796</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1372</v>
+        <v>0.2141</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4395</v>
+        <v>0.0391</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5767</v>
+        <v>0.175</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7935</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
         <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.6805</v>
+        <v>-1.668</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3602</v>
+        <v>-1.0088</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.3203</v>
+        <v>-0.6592</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1352</v>
+        <v>3.6194</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1352</v>
+        <v>3.5481</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>,. VICENTE SABARIEGO</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1029,40 +1029,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1948</v>
+        <v>-0.2292</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7935</v>
+        <v>-0.9023</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9883</v>
+        <v>0.6731</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.6767</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.2621</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.4146</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7566000000000001</v>
+        <v>-0.0149</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7566000000000001</v>
+        <v>-0.0149</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.6916</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.277</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.4146</v>
       </c>
       <c r="P8" t="n">
         <v>-0.9919</v>
@@ -1074,28 +1074,28 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2588</v>
+        <v>-0.5172</v>
       </c>
       <c r="T8" t="n">
-        <v>2.0406</v>
+        <v>-0.4988</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2182</v>
+        <v>-0.0185</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.2182</v>
+        <v>0.6032</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.0118</v>
+        <v>0.6032</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>P. SAIZ FUENTES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1107,73 +1107,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4256</v>
+        <v>-1.1158</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9023</v>
+        <v>-1.0554</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4767</v>
+        <v>-0.0604</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6767</v>
+        <v>0.6793</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2621</v>
+        <v>1.8997</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4146</v>
+        <v>-1.2204</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0149</v>
+        <v>-0.7348</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0149</v>
+        <v>1.8655</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-2.6003</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6916</v>
+        <v>1.4141</v>
       </c>
       <c r="N9" t="n">
-        <v>0.277</v>
+        <v>0.0342</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4146</v>
+        <v>1.3799</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9919</v>
+        <v>0.9919</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7136</v>
+        <v>-2.1837</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4988</v>
+        <v>-0.9238</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2148</v>
+        <v>-1.2599</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6032</v>
+        <v>-0.6032</v>
       </c>
       <c r="W9" t="n">
         <v>0.6032</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. SAIZ FUENTES</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1185,64 +1185,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1806</v>
+        <v>-1.5126</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8116</v>
+        <v>-0.4309</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.369</v>
+        <v>-1.0818</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6793</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8997</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2204</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7348</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8655</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.6003</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4141</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0342</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3799</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9919</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9919</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.2486</v>
+        <v>0.9409</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.68</v>
+        <v>0.8162</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5685</v>
+        <v>0.1247</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6032</v>
+        <v>-2.2182</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6032</v>
+        <v>-1.0118</v>
       </c>
       <c r="X10" t="n">
         <v>-1.2065</v>
@@ -1263,13 +1263,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8359</v>
+        <v>-1.5477</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1286</v>
+        <v>-0.9245</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7074</v>
+        <v>-0.6232</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1722</v>
@@ -1308,13 +1308,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6557</v>
+        <v>-1.3674</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7991</v>
+        <v>-0.5951</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8565</v>
+        <v>-0.7723</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ FLAQUE</t>
+          <t>M. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1341,73 +1341,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2763</v>
+        <v>-2.045</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.676</v>
+        <v>-4.9734</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6002999999999999</v>
+        <v>2.9284</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4087</v>
+        <v>-0.5594</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7209</v>
+        <v>-2.7216</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3122</v>
+        <v>2.1622</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2396</v>
+        <v>-1.0965</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5995</v>
+        <v>-1.4708</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.64</v>
+        <v>0.3742</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8309</v>
+        <v>0.5372</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1214</v>
+        <v>-1.2508</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9523</v>
+        <v>1.788</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9919</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9919</v>
+        <v>2.1822</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0498</v>
+        <v>-0.8347</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4364</v>
+        <v>-0.9011</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6133999999999999</v>
+        <v>0.0664</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8097</v>
+        <v>0.1425</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.8097</v>
+        <v>0.1425</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. MAÑES CARRETERO</t>
+          <t>G. RODRIGUEZ FLAQUE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1419,67 +1419,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4058</v>
+        <v>-2.1844</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.1378</v>
+        <v>-1.4719</v>
       </c>
       <c r="F13" t="n">
-        <v>2.732</v>
+        <v>-0.7125</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5594</v>
+        <v>-0.4087</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.7216</v>
+        <v>-0.7209</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1622</v>
+        <v>0.3122</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0965</v>
+        <v>-1.2396</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4708</v>
+        <v>-0.5995</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3742</v>
+        <v>-0.64</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5372</v>
+        <v>0.8309</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2508</v>
+        <v>-0.1214</v>
       </c>
       <c r="O13" t="n">
-        <v>1.788</v>
+        <v>0.9523</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1822</v>
+        <v>0.9919</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1954</v>
+        <v>-0.9579</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0655</v>
+        <v>-0.2324</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.13</v>
+        <v>-0.7256</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1425</v>
+        <v>-1.8097</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1425</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="14">
@@ -1497,13 +1497,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.1889</v>
+        <v>-6.1787</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.5574</v>
+        <v>-5.6594</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6315</v>
+        <v>-0.5193</v>
       </c>
       <c r="G14" t="n">
         <v>-4.4957</v>
@@ -1542,13 +1542,13 @@
         <v>1.1903</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6337</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2436</v>
+        <v>-0.3457</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.39</v>
+        <v>-0.2778</v>
       </c>
       <c r="V14" t="n">
         <v>-0.266</v>
@@ -1575,28 +1575,28 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.7865</v>
+        <v>-3.314399999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-15.2198</v>
+        <v>-14.1318</v>
       </c>
       <c r="F15" t="n">
-        <v>10.4336</v>
+        <v>10.8169</v>
       </c>
       <c r="G15" t="n">
-        <v>3.303399999999999</v>
+        <v>3.303400000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9816999999999991</v>
+        <v>0.9816999999999996</v>
       </c>
       <c r="I15" t="n">
-        <v>2.322</v>
+        <v>2.321999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.8295</v>
+        <v>-1.829500000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>6.3826</v>
+        <v>6.382599999999998</v>
       </c>
       <c r="L15" t="n">
         <v>-8.2121</v>
@@ -1605,7 +1605,7 @@
         <v>5.1331</v>
       </c>
       <c r="N15" t="n">
-        <v>-5.4008</v>
+        <v>-5.400800000000001</v>
       </c>
       <c r="O15" t="n">
         <v>10.5339</v>
@@ -1620,16 +1620,16 @@
         <v>14.6803</v>
       </c>
       <c r="S15" t="n">
-        <v>-12.943</v>
+        <v>-11.4712</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.837800000000001</v>
+        <v>-6.7498</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.105</v>
+        <v>-4.7216</v>
       </c>
       <c r="V15" t="n">
-        <v>2.075699999999999</v>
+        <v>2.0757</v>
       </c>
       <c r="W15" t="n">
         <v>6.3504</v>
@@ -1653,13 +1653,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.593</v>
+        <v>7.9576</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0843</v>
+        <v>4.3087</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5087</v>
+        <v>3.649</v>
       </c>
       <c r="G16" t="n">
         <v>3.1918</v>
@@ -1698,13 +1698,13 @@
         <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8134</v>
+        <v>0.5513</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5359</v>
+        <v>-0.3116</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7226</v>
+        <v>0.8628</v>
       </c>
       <c r="V16" t="n">
         <v>3.6194</v>
@@ -1719,7 +1719,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>P. SARRATE CARRILLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1731,73 +1731,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6116</v>
+        <v>2.6721</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9724</v>
+        <v>0.1136</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6393</v>
+        <v>2.5585</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4137</v>
+        <v>1.3166</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8566</v>
+        <v>-0.7057</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5572</v>
+        <v>2.0222</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0484</v>
+        <v>0.1762</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0484</v>
+        <v>-0.2006</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.3768</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3653</v>
+        <v>1.1404</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1918</v>
+        <v>-0.5051</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5572</v>
+        <v>1.6455</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1984</v>
+        <v>1.5871</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8687</v>
+        <v>1.9669</v>
       </c>
       <c r="T17" t="n">
-        <v>0.924</v>
+        <v>0.6634</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9448</v>
+        <v>1.3035</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8692</v>
+        <v>-1.2065</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8692</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. SARRATE CARRILLO</t>
+          <t>C. DICKERSON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1809,73 +1809,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2708</v>
+        <v>2.4503</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6006</v>
+        <v>1.2475</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8714</v>
+        <v>1.2028</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3166</v>
+        <v>1.7574</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7057</v>
+        <v>2.8171</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0222</v>
+        <v>-1.0598</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1762</v>
+        <v>2.2511</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2006</v>
+        <v>2.9287</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3768</v>
+        <v>-0.6776</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1404</v>
+        <v>-0.4937</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5051</v>
+        <v>-0.1116</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6455</v>
+        <v>-0.3821</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5952</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5655</v>
+        <v>1.4865</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0509</v>
+        <v>0.7143</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6163</v>
+        <v>0.7722</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0.266</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4724</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. PARADEDA VIDAL</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1887,67 +1887,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6178</v>
+        <v>1.6909</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8854</v>
+        <v>1.3602</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7323</v>
+        <v>0.3306</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7887</v>
+        <v>1.4137</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3774</v>
+        <v>0.8566</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1661</v>
+        <v>0.5572</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3334</v>
+        <v>1.0484</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1326</v>
+        <v>1.0484</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2008</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4553</v>
+        <v>0.3653</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.51</v>
+        <v>-0.1918</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9653</v>
+        <v>0.5572</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="S19" t="n">
-        <v>3.7615</v>
+        <v>0.948</v>
       </c>
       <c r="T19" t="n">
-        <v>2.6586</v>
+        <v>0.3118</v>
       </c>
       <c r="U19" t="n">
-        <v>1.1029</v>
+        <v>0.6362</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5437</v>
+        <v>-0.8692</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4129</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2538</v>
+        <v>0.7674</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1857</v>
+        <v>-1.6959</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4395</v>
+        <v>2.4633</v>
       </c>
       <c r="G20" t="n">
         <v>0.3253</v>
@@ -2010,13 +2010,13 @@
         <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9204</v>
+        <v>1.434</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0544</v>
+        <v>0.5443</v>
       </c>
       <c r="U20" t="n">
-        <v>0.866</v>
+        <v>0.8898</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. DICKERSON</t>
+          <t>E. PARADEDA VIDAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,67 +2043,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0415</v>
+        <v>0.101</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2272</v>
+        <v>-0.543</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8143</v>
+        <v>0.6439</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7574</v>
+        <v>0.7887</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8171</v>
+        <v>-0.3774</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0598</v>
+        <v>1.1661</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2511</v>
+        <v>0.3334</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9287</v>
+        <v>0.1326</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6776</v>
+        <v>0.2008</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4937</v>
+        <v>0.4553</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1116</v>
+        <v>-0.51</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3821</v>
+        <v>0.9653</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7935</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>0.07770000000000001</v>
+        <v>2.2446</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.306</v>
+        <v>1.2302</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3837</v>
+        <v>1.0145</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.5437</v>
       </c>
       <c r="W21" t="n">
-        <v>0.266</v>
+        <v>0.8692</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.266</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="22">
@@ -2121,13 +2121,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0394</v>
+        <v>-0.083</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7977</v>
+        <v>-2.6957</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8371</v>
+        <v>2.6127</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5964</v>
@@ -2166,13 +2166,13 @@
         <v>1.1903</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4374</v>
+        <v>1.315</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4366</v>
+        <v>0.5386</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0009</v>
+        <v>0.7764</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2199,58 +2199,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2665</v>
+        <v>-1.2326</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7742</v>
+        <v>-1.9084</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5077</v>
+        <v>0.6758</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2568</v>
+        <v>-2.3067</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0454</v>
+        <v>-1.2651</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2113</v>
+        <v>-1.0416</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0123</v>
+        <v>-1.9198</v>
       </c>
       <c r="K23" t="n">
-        <v>0.348</v>
+        <v>-0.5995</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3604</v>
+        <v>-1.3202</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2444</v>
+        <v>-0.387</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3935</v>
+        <v>-0.6655</v>
       </c>
       <c r="O23" t="n">
-        <v>0.149</v>
+        <v>0.2786</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="S23" t="n">
-        <v>1.9822</v>
+        <v>0.479</v>
       </c>
       <c r="T23" t="n">
-        <v>2.222</v>
+        <v>0.0114</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2398</v>
+        <v>0.4676</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2265,7 +2265,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2277,58 +2277,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0233</v>
+        <v>-1.6464</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4185</v>
+        <v>-2.4066</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3952</v>
+        <v>0.7602</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.3067</v>
+        <v>-1.2568</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2651</v>
+        <v>-0.0454</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0416</v>
+        <v>-1.2113</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.9198</v>
+        <v>-1.0123</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5995</v>
+        <v>0.348</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3202</v>
+        <v>-1.3604</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.387</v>
+        <v>-0.2444</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6655</v>
+        <v>-0.3935</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2786</v>
+        <v>0.149</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5952</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3117</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4988</v>
+        <v>0.5896</v>
       </c>
       <c r="U24" t="n">
-        <v>0.187</v>
+        <v>0.0127</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2355,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9659</v>
+        <v>-2.2976</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0495</v>
+        <v>-2.4373</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.1397</v>
       </c>
       <c r="G25" t="n">
         <v>-3.213</v>
@@ -2400,13 +2400,13 @@
         <v>0.5952</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.348</v>
+        <v>0.3203</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5611</v>
+        <v>0.0511</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2131</v>
+        <v>0.2692</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.8227</v>
+        <v>-3.35</v>
       </c>
       <c r="E26" t="n">
         <v>-3.685</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1377</v>
+        <v>0.335</v>
       </c>
       <c r="G26" t="n">
         <v>-2.8785</v>
@@ -2478,13 +2478,13 @@
         <v>1.3887</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7347</v>
+        <v>1.2074</v>
       </c>
       <c r="T26" t="n">
         <v>0.5047</v>
       </c>
       <c r="U26" t="n">
-        <v>0.23</v>
+        <v>0.7027</v>
       </c>
       <c r="V26" t="n">
         <v>-2.0757</v>
@@ -2511,13 +2511,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>6.349500000000002</v>
+        <v>7.0297</v>
       </c>
       <c r="E27" t="n">
         <v>-8.341900000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>14.6914</v>
+        <v>15.3715</v>
       </c>
       <c r="G27" t="n">
         <v>-2.4579</v>
@@ -2526,7 +2526,7 @@
         <v>-1.7126</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.7452000000000001</v>
+        <v>-0.7452000000000005</v>
       </c>
       <c r="J27" t="n">
         <v>-4.5693</v>
@@ -2541,10 +2541,10 @@
         <v>2.1114</v>
       </c>
       <c r="N27" t="n">
-        <v>-6.180899999999999</v>
+        <v>-6.1809</v>
       </c>
       <c r="O27" t="n">
-        <v>8.292499999999999</v>
+        <v>8.2925</v>
       </c>
       <c r="P27" t="n">
         <v>-0.9916000000000003</v>
@@ -2556,13 +2556,13 @@
         <v>11.9032</v>
       </c>
       <c r="S27" t="n">
-        <v>11.875</v>
+        <v>12.5553</v>
       </c>
       <c r="T27" t="n">
-        <v>4.8476</v>
+        <v>4.847799999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>7.0275</v>
+        <v>7.707599999999999</v>
       </c>
       <c r="V27" t="n">
         <v>-2.075699999999999</v>
@@ -2571,7 +2571,7 @@
         <v>4.2748</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.3504</v>
+        <v>-6.350399999999999</v>
       </c>
     </row>
   </sheetData>
